--- a/design_issues/sonarqube/P2_VocabularyApp.xlsx
+++ b/design_issues/sonarqube/P2_VocabularyApp.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
     <sheet name="Stats" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -9420,6 +9420,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B30">
+        <f>SUM(B2:B29)</f>
         <v>350</v>
       </c>
     </row>
